--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-perf-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-perf-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Kiểm thử hiệu năng là kiểm thử phi chức năng, đánh giá các đặc tính tốc độ, độ ổn định và tài nguyên hệ thống tiêu thụ dưới các mức tải khác nhau.</v>
       </c>
       <c r="F2" t="str">
-        <v>Đánh giá tốc độ phản hồi, độ ổn định, độ tin cậy và khả năng mở rộng của hệ thống dưới các điều kiện tải khác nhau — đánh giá vận hành dưới tải</v>
+        <v>Kiểm tra xem các thuật toán mã hóa mật khẩu của hệ thống có bị bẻ khóa hay không — kiểm thử bảo mật mật khẩu</v>
       </c>
       <c r="G2" t="str">
         <v>Tìm kiếm các lỗi viết sai chính tả hoặc sai lệch màu sắc hiển thị trên giao diện — kiểm tra giao diện và chính tả</v>
       </c>
       <c r="H2" t="str">
-        <v>Kiểm tra xem các thuật toán mã hóa mật khẩu của hệ thống có bị bẻ khóa hay không — kiểm thử bảo mật mật khẩu</v>
+        <v>Đánh giá tốc độ phản hồi, độ ổn định, độ tin cậy và khả năng mở rộng của hệ thống dưới các điều kiện tải khác nhau — đánh giá vận hành dưới tải</v>
       </c>
       <c r="I2" t="str">
         <v>Xây dựng các kịch bản kiểm thử tự động cho luồng đăng ký tài khoản — kiểm thử tự động chức năng</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>Khoảng thời gian kể từ khi người dùng gửi yêu cầu (Request) cho đến khi nhận được phản hồi (Response) hoàn chỉnh từ hệ thống — thời gian gửi nhận yêu cầu phản hồi</v>
       </c>
       <c r="G3" t="str">
+        <v>Tổng thời gian chạy toàn bộ bộ kịch bản kiểm thử tự động của dự án — thời gian chạy test suite</v>
+      </c>
+      <c r="H3" t="str">
         <v>Thời gian lập trình viên cần để sửa xong một lỗi nghiêm trọng trong mã nguồn — thời gian sửa lỗi của dev</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Số giây tối đa trình duyệt web hiển thị màn hình trống trước khi bắt đầu tải trang — thời gian tải trang trống</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Tổng thời gian chạy toàn bộ bộ kịch bản kiểm thử tự động của dự án — thời gian chạy test suite</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -524,19 +524,19 @@
         <v>Throughput (thông lượng) thể hiện năng lực tải của hệ thống. Thông lượng cao và ổn định chứng tỏ hệ thống xử lý song song tốt.</v>
       </c>
       <c r="F4" t="str">
+        <v>Kích thước dung lượng file cài đặt của ứng dụng di động trên bộ nhớ máy — dung lượng file cài</v>
+      </c>
+      <c r="G4" t="str">
         <v>Số lượng yêu cầu (Requests) hoặc lượng dữ liệu hệ thống có thể xử lý thành công trong một đơn vị thời gian (ví dụ: requests/giây) — băng thông xử lý yêu cầu</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Tổng số lỗi bảo mật được quét và phát hiện thành công trong mã nguồn — số lượng lỗi bảo mật</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>Số lượng test case tối đa một tester có thể chạy thủ công trong một ngày — năng suất chạy test tay</v>
       </c>
-      <c r="I4" t="str">
-        <v>Kích thước dung lượng file cài đặt của ứng dụng di động trên bộ nhớ máy — dung lượng file cài</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Thread Group trong JMeter đại diện cho nhóm người dùng ảo. Cấu hình số Threads chính là cấu hình số Virtual Users (VUs) tham gia tải.</v>
       </c>
       <c r="F5" t="str">
+        <v>Địa chỉ URL và phương thức gọi API (GET, POST) cần kiểm thử — cấu hình endpoint API</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Các câu lệnh truy vấn dữ liệu SQL cần chạy trong cơ sở dữ liệu — cấu hình truy vấn database</v>
+      </c>
+      <c r="H5" t="str">
         <v>Số lượng người dùng giả lập (Virtual Users), thời gian tăng tải (Ramp-up period) và số vòng lặp chạy test — cấu hình người dùng giả lập</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Địa chỉ URL và phương thức gọi API (GET, POST) cần kiểm thử — cấu hình endpoint API</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Các câu lệnh truy vấn dữ liệu SQL cần chạy trong cơ sở dữ liệu — cấu hình truy vấn database</v>
       </c>
       <c r="I5" t="str">
         <v>Biểu đồ trực quan hiển thị kết quả thời gian phản hồi dưới dạng đồ thị — cấu hình biểu đồ hiển thị</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Hàm `COUNT(*)` trong SQL dùng để đếm số lượng dòng thỏa mãn điều kiện trong bảng dữ liệu.</v>
       </c>
       <c r="F6" t="str">
-        <v>SELECT COUNT(*) FROM table_name; — câu lệnh đếm tổng bản ghi</v>
+        <v>SELECT MAX(*) FROM table_name; — câu lệnh tìm giá trị lớn nhất</v>
       </c>
       <c r="G6" t="str">
         <v>SELECT SUM(*) FROM table_name; — câu lệnh tính tổng giá trị số</v>
       </c>
       <c r="H6" t="str">
-        <v>SELECT MAX(*) FROM table_name; — câu lệnh tìm giá trị lớn nhất</v>
+        <v>SELECT LIMIT(*) FROM table_name; — câu lệnh giới hạn dòng trả về</v>
       </c>
       <c r="I6" t="str">
-        <v>SELECT LIMIT(*) FROM table_name; — câu lệnh giới hạn dòng trả về</v>
+        <v>SELECT COUNT(*) FROM table_name; — câu lệnh đếm tổng bản ghi</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Để đảm bảo tính độc lập và không làm bẩn dữ liệu môi trường test, sau khi chạy các test case thực hiện ghi dữ liệu (INSERT/UPDATE/DELETE), QA gọi `ROLLBACK` để hoàn tác giao dịch.</v>
       </c>
       <c r="F7" t="str">
+        <v>Tự động sao lưu dữ liệu của bảng sang một máy chủ dự phòng khác — sao lưu dự phòng</v>
+      </c>
+      <c r="G7" t="str">
         <v>Hủy bỏ các thay đổi dữ liệu vừa thực hiện trong giao dịch (Transaction) để trả database về trạng thái sạch ban đầu — rollback trả về trạng thái cũ</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
+        <v>Mã hóa các mật khẩu của tài khoản vừa được tạo trong bảng người dùng — mã hóa mật khẩu</v>
+      </c>
+      <c r="I7" t="str">
         <v>Xác nhận và lưu vĩnh viễn các thay đổi dữ liệu đó vào trong ổ cứng máy chủ — commit lưu dữ liệu</v>
       </c>
-      <c r="H7" t="str">
-        <v>Tự động sao lưu dữ liệu của bảng sang một máy chủ dự phòng khác — sao lưu dự phòng</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Mã hóa các mật khẩu của tài khoản vừa được tạo trong bảng người dùng — mã hóa mật khẩu</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -655,13 +655,13 @@
         <v>Thu thập, phân tích và hiển thị kết quả kiểm thử hiệu năng dưới dạng bảng biểu hoặc đồ thị trực quan — thu thập hiển thị kết quả</v>
       </c>
       <c r="G8" t="str">
+        <v>Chèn các tham số dữ liệu ngẫu nhiên vào trong thân của request gửi đi — chèn tham số dữ liệu</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Tự động tắt trình duyệt web khi phát sinh lỗi quá tải trên máy chủ — tắt trình duyệt</v>
+      </c>
+      <c r="I8" t="str">
         <v>Gửi các request HTTP lên máy chủ để giả lập tải người dùng — giả lập tải gửi request</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Chèn các tham số dữ liệu ngẫu nhiên vào trong thân của request gửi đi — chèn tham số dữ liệu</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Tự động tắt trình duyệt web khi phát sinh lỗi quá tải trên máy chủ — tắt trình duyệt</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -684,19 +684,19 @@
         <v>Từ khóa `DISTINCT` đi sau SELECT dùng để loại bỏ các dòng trùng lặp trong tập kết quả trả về của truy vấn.</v>
       </c>
       <c r="F9" t="str">
-        <v>DISTINCT — ví dụ `SELECT DISTINCT category` lấy các danh mục độc nhất — lọc trùng DISTINCT</v>
+        <v>ORDER BY — sắp xếp thứ tự hiển thị của các dòng dữ liệu trả về — sắp xếp ORDER BY</v>
       </c>
       <c r="G9" t="str">
         <v>UNIQUE — ràng buộc tính duy nhất của cột khi tạo bảng — ràng buộc UNIQUE</v>
       </c>
       <c r="H9" t="str">
+        <v>DISTINCT — ví dụ `SELECT DISTINCT category` lấy các danh mục độc nhất — lọc trùng DISTINCT</v>
+      </c>
+      <c r="I9" t="str">
         <v>GROUP BY — gom nhóm các hàng có cùng giá trị để thực hiện hàm tổng hợp — gom nhóm GROUP BY</v>
       </c>
-      <c r="I9" t="str">
-        <v>ORDER BY — sắp xếp thứ tự hiển thị của các dòng dữ liệu trả về — sắp xếp ORDER BY</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Database testing kiểm tra xem dữ liệu được lưu trữ, cập nhật và xóa đúng logic nghiệp vụ ở tầng DB (không chỉ kiểm tra trên giao diện hiển thị).</v>
       </c>
       <c r="F10" t="str">
+        <v>Tốc độ gõ phím của lập trình viên khi viết mã nguồn các stored procedures — tốc độ gõ phím</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Khả năng chống đỡ các cuộc tấn công vật lý vào phòng chứa máy chủ của bệnh viện — bảo vệ vật lý máy chủ</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Màu sắc của các bảng hiển thị thông tin số dư trên màn hình ứng dụng di động — thiết kế bảng UI</v>
+      </c>
+      <c r="I10" t="str">
         <v>Tính toàn vẹn dữ liệu, tính chính xác của các mối quan hệ bảng, các ràng buộc và dữ liệu lưu trữ thực tế so với đặc tả — xác thực toàn vẹn dữ liệu</v>
       </c>
-      <c r="G10" t="str">
-        <v>Màu sắc của các bảng hiển thị thông tin số dư trên màn hình ứng dụng di động — thiết kế bảng UI</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Tốc độ gõ phím của lập trình viên khi viết mã nguồn các stored procedures — tốc độ gõ phím</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Khả năng chống đỡ các cuộc tấn công vật lý vào phòng chứa máy chủ của bệnh viện — bảo vệ vật lý máy chủ</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>CPU Usage 100% liên tục chứng tỏ năng lực tính toán của server đã đạt giới hạn. Yêu cầu xử lý sẽ bị xếp hàng (queue), làm tăng vọt Response Time của người dùng.</v>
       </c>
       <c r="F11" t="str">
-        <v>Bộ vi xử lý của máy chủ đang bị quá tải, có thể gây nghẽn cổ chai và làm chậm hoặc sập hệ thống — quá tải bộ vi xử lý</v>
+        <v>Toàn bộ dung lượng ổ cứng vật lý của máy chủ đã bị đầy không thể ghi thêm file — đầy ổ cứng</v>
       </c>
       <c r="G11" t="str">
         <v>Máy chủ đang hoạt động cực kỳ mát và tiết kiệm tối đa năng lượng tiêu thụ — tiết kiệm năng lượng</v>
       </c>
       <c r="H11" t="str">
-        <v>Toàn bộ dung lượng ổ cứng vật lý của máy chủ đã bị đầy không thể ghi thêm file — đầy ổ cứng</v>
+        <v>Bộ vi xử lý của máy chủ đang bị quá tải, có thể gây nghẽn cổ chai và làm chậm hoặc sập hệ thống — quá tải bộ vi xử lý</v>
       </c>
       <c r="I11" t="str">
         <v>Hệ thống mạng internet của công ty đang có tốc độ truyền tải nhanh nhất lịch sử — tốc độ mạng nhanh</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
